--- a/Outputs/Scenarios/PtX_demand_SI_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_SI_Electrification.xlsx
@@ -1555,7 +1555,7 @@
         <v>0.001414363771599922</v>
       </c>
       <c r="K30" t="n">
-        <v>0.00342535338808826</v>
+        <v>0.003425353388088259</v>
       </c>
     </row>
     <row r="31">
@@ -1568,7 +1568,7 @@
         <v>2050</v>
       </c>
       <c r="C31" t="n">
-        <v>0.000624812994694416</v>
+        <v>0.0006248129946944161</v>
       </c>
       <c r="D31" t="n">
         <v>0.0004005438820642003</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0005708922313480434</v>
+        <v>0.0005708922313480433</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.002283568925392174</v>
+        <v>0.002283568925392173</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.00342535338808826</v>
+        <v>0.003425353388088259</v>
       </c>
     </row>
     <row r="34">
@@ -1975,7 +1975,7 @@
         <v>2050</v>
       </c>
       <c r="C42" t="n">
-        <v>0.000312406497347208</v>
+        <v>0.0003124064973472081</v>
       </c>
       <c r="D42" t="n">
         <v>0.0003204351056513603</v>
@@ -1999,7 +1999,7 @@
         <v>7.444019850525905e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0005708922313480434</v>
+        <v>0.0005708922313480433</v>
       </c>
     </row>
     <row r="43">

--- a/Outputs/Scenarios/PtX_demand_SI_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_SI_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.000955407017199607</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0005817580435385498</v>
+        <v>0.0006187407329528117</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>9.695967392309164e-05</v>
+        <v>0.0001285076906901994</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0003878386956923666</v>
+        <v>0.0005140307627607976</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0005817580435385498</v>
+        <v>0.0005140307627607976</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>7.656649653298931e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0008050748728253992</v>
+        <v>0.0007903882522875483</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.0004634571645962034</v>
       </c>
       <c r="K25" t="n">
-        <v>0.007885787344867851</v>
+        <v>0.007741930456166546</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>1.376579788500048e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>9.695967392309164e-05</v>
+        <v>0.0001285076906901994</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.001414363771599922</v>
       </c>
       <c r="K30" t="n">
-        <v>0.003425353388088259</v>
+        <v>0.003339719553386053</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0005708922313480433</v>
+        <v>0.0006936340610878728</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.002283568925392173</v>
+        <v>0.002774536244351491</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.003425353388088259</v>
+        <v>0.002774536244351491</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>7.444019850525905e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0005708922313480433</v>
+        <v>0.0006936340610878728</v>
       </c>
     </row>
     <row r="43">
